--- a/data/trans_orig/IP31KM06_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP31KM06_2023-Provincia-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>16659</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>11466</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>23797</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>27,64%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>19,03%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>39,49%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>10566</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>6630</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>17023</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>14,8%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>9,29%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>23,84%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>19319</t>
+          <t>10009</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>13035</t>
+          <t>6005</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>27458</t>
+          <t>14480</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>25,89%</t>
+          <t>18,22%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>36,8%</t>
+          <t>26,37%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>29886</t>
+          <t>26668</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>22259</t>
+          <t>19849</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>40157</t>
+          <t>34410</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>23,15%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>17,23%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>27,5%</t>
+          <t>29,87%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>43604</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>36466</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>48797</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>72,36%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>60,51%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>80,97%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>75</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>60834</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>54377</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>64770</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>85,2%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>76,16%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>90,71%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>55288</t>
+          <t>44913</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>47149</t>
+          <t>40442</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>61572</t>
+          <t>48917</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>74,11%</t>
+          <t>81,78%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>63,2%</t>
+          <t>73,63%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>82,53%</t>
+          <t>89,07%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>116121</t>
+          <t>88518</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>105850</t>
+          <t>80776</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>123748</t>
+          <t>95337</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>79,53%</t>
+          <t>76,85%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>72,5%</t>
+          <t>70,13%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>84,76%</t>
+          <t>82,77%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>60263</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>60263</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>60263</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>92</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>71400</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>71400</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>71400</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>74607</t>
+          <t>54922</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>74607</t>
+          <t>54922</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>74607</t>
+          <t>54922</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>146007</t>
+          <t>115186</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>146007</t>
+          <t>115186</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>146007</t>
+          <t>115186</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>57415</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>46731</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>67498</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>49,95%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>40,65%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>58,72%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>54</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>68675</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>48835</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>101700</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>54,66%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>38,87%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>80,94%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>62222</t>
+          <t>42786</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>50417</t>
+          <t>33942</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>73971</t>
+          <t>52052</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>49,22%</t>
+          <t>43,07%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>39,88%</t>
+          <t>34,17%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>58,51%</t>
+          <t>52,4%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>130897</t>
+          <t>100201</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>107766</t>
+          <t>85435</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>167582</t>
+          <t>113873</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>51,93%</t>
+          <t>46,76%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>42,75%</t>
+          <t>39,87%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>66,48%</t>
+          <t>53,14%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>57536</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>47453</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>68220</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>50,05%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>41,28%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>59,35%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>86</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>56974</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>23949</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>76814</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>45,34%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>19,06%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>61,13%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>64201</t>
+          <t>56547</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>52452</t>
+          <t>47281</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>76006</t>
+          <t>65391</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>50,78%</t>
+          <t>56,93%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>41,49%</t>
+          <t>47,6%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>60,12%</t>
+          <t>65,83%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>121174</t>
+          <t>114083</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>84489</t>
+          <t>100411</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>144305</t>
+          <t>128849</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>48,07%</t>
+          <t>53,24%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>33,52%</t>
+          <t>46,86%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>57,25%</t>
+          <t>60,13%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>114951</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>114951</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>114951</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>140</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>125649</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>125649</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>125649</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>153</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>126423</t>
+          <t>99333</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>126423</t>
+          <t>99333</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>126423</t>
+          <t>99333</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>252071</t>
+          <t>214284</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>252071</t>
+          <t>214284</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>252071</t>
+          <t>214284</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>17046</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>11659</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>22464</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>29,75%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>20,35%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>39,21%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>18426</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>13223</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>24310</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>33,17%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>23,8%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>43,76%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>19446</t>
+          <t>18199</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>13788</t>
+          <t>12643</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>26207</t>
+          <t>23540</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>30,09%</t>
+          <t>33,63%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>23,36%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>40,55%</t>
+          <t>43,5%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>37872</t>
+          <t>35245</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>30122</t>
+          <t>27838</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>46090</t>
+          <t>42657</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>31,51%</t>
+          <t>31,63%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>25,06%</t>
+          <t>24,99%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>38,35%</t>
+          <t>38,29%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>40253</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>34835</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>45640</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>70,25%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>60,79%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>79,65%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>61</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>37126</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>31242</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>42329</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>66,83%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>56,24%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>76,2%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>45187</t>
+          <t>35913</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>38426</t>
+          <t>30572</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>50845</t>
+          <t>41469</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>69,91%</t>
+          <t>66,37%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>59,45%</t>
+          <t>56,5%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>78,67%</t>
+          <t>76,64%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>82313</t>
+          <t>76166</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>74095</t>
+          <t>68754</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>90063</t>
+          <t>83573</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>68,49%</t>
+          <t>68,37%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>61,65%</t>
+          <t>61,71%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>74,94%</t>
+          <t>75,01%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>57299</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>57299</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>57299</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>91</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>55552</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>55552</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>55552</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>64633</t>
+          <t>54112</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>64633</t>
+          <t>54112</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>64633</t>
+          <t>54112</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>120185</t>
+          <t>111411</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>120185</t>
+          <t>111411</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>120185</t>
+          <t>111411</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>20454</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>10574</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>38596</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>29,3%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>15,15%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>55,28%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>20639</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>13974</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>27853</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>29,62%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>20,05%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>39,97%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>23154</t>
+          <t>21388</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11194</t>
+          <t>15120</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>46023</t>
+          <t>28782</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>30,72%</t>
+          <t>30,35%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>21,46%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>61,07%</t>
+          <t>40,85%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>43793</t>
+          <t>41842</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>31007</t>
+          <t>30896</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>72023</t>
+          <t>62814</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>30,19%</t>
+          <t>29,83%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,38%</t>
+          <t>22,02%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>49,65%</t>
+          <t>44,78%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>49362</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>31220</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>59242</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>70,7%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>44,72%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>84,85%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>66</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>49043</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>41829</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>55708</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>70,38%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>60,03%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>79,95%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>52213</t>
+          <t>49074</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>29344</t>
+          <t>41680</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>64173</t>
+          <t>55342</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>69,28%</t>
+          <t>69,65%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>38,93%</t>
+          <t>59,15%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,15%</t>
+          <t>78,54%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>101256</t>
+          <t>98436</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>73026</t>
+          <t>77464</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>114042</t>
+          <t>109382</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>69,81%</t>
+          <t>70,17%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>50,35%</t>
+          <t>55,22%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>78,62%</t>
+          <t>77,98%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>69816</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>69816</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>69816</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>93</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>69682</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>69682</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>69682</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>75367</t>
+          <t>70462</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>75367</t>
+          <t>70462</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>75367</t>
+          <t>70462</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>145049</t>
+          <t>140278</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>145049</t>
+          <t>140278</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>145049</t>
+          <t>140278</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,72 +2092,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>9331</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>5706</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>13858</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>23,57%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>14,42%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>35,01%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>2793</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>1099</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>5770</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>8,17%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>3,21%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>16,87%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>9445</t>
+          <t>2981</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5763</t>
+          <t>1043</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>13787</t>
+          <t>6008</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>33,86%</t>
+          <t>16,99%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>12239</t>
+          <t>12312</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8300</t>
+          <t>7910</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>18116</t>
+          <t>17439</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>23,27%</t>
         </is>
       </c>
     </row>
@@ -2205,72 +2205,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>30248</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>25721</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>33873</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>76,43%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>64,99%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>85,58%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>61</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>31407</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>28430</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>33101</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>91,83%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>83,13%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>96,79%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>31274</t>
+          <t>32389</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>26932</t>
+          <t>29362</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>34956</t>
+          <t>34327</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>76,8%</t>
+          <t>91,57%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>66,14%</t>
+          <t>83,01%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>85,85%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>62680</t>
+          <t>62637</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>56803</t>
+          <t>57510</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>66619</t>
+          <t>67039</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>83,66%</t>
+          <t>83,57%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>75,82%</t>
+          <t>76,73%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>88,92%</t>
+          <t>89,45%</t>
         </is>
       </c>
     </row>
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>34200</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>34200</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>34200</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>35370</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>35370</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>35370</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>74919</t>
+          <t>74949</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>74919</t>
+          <t>74949</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>74919</t>
+          <t>74949</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2435,72 +2435,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>10144</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>6348</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>14823</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>21,49%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>13,45%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>31,4%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>10655</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>6824</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>15581</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>24,06%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>15,41%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>35,18%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>11449</t>
+          <t>11064</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>7130</t>
+          <t>7337</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>17276</t>
+          <t>16025</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>21,29%</t>
+          <t>24,98%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>32,12%</t>
+          <t>36,19%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>22104</t>
+          <t>21208</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>16230</t>
+          <t>15230</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>29203</t>
+          <t>27976</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>23,18%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>29,78%</t>
+          <t>30,58%</t>
         </is>
       </c>
     </row>
@@ -2548,72 +2548,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>37065</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>32386</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>40861</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>78,51%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>68,6%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>86,55%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>56</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>33635</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>28709</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>37466</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>75,94%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>64,82%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>84,59%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>42333</t>
+          <t>33222</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>36506</t>
+          <t>28261</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>46652</t>
+          <t>36949</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>78,71%</t>
+          <t>75,02%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>67,88%</t>
+          <t>63,81%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>86,74%</t>
+          <t>83,43%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>75968</t>
+          <t>70287</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>68869</t>
+          <t>63519</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>81842</t>
+          <t>76265</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>77,46%</t>
+          <t>76,82%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>70,22%</t>
+          <t>69,42%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>83,45%</t>
+          <t>83,35%</t>
         </is>
       </c>
     </row>
@@ -2661,57 +2661,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>47209</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>47209</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>47209</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>74</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>44290</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>44290</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>44290</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>53782</t>
+          <t>44286</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>53782</t>
+          <t>44286</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>53782</t>
+          <t>44286</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>98072</t>
+          <t>91495</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>98072</t>
+          <t>91495</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>98072</t>
+          <t>91495</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2778,72 +2778,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>53622</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>41406</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>64723</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>38,15%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>29,46%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>46,04%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>57</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>40073</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>31792</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>49763</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>32,4%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>25,7%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>40,23%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>60070</t>
+          <t>42300</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>48599</t>
+          <t>33617</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>73509</t>
+          <t>50551</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>38,74%</t>
+          <t>34,72%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>31,35%</t>
+          <t>27,59%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>47,41%</t>
+          <t>41,5%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>100143</t>
+          <t>95921</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>85592</t>
+          <t>82138</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>116833</t>
+          <t>109984</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>35,93%</t>
+          <t>36,56%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>30,71%</t>
+          <t>31,3%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>41,91%</t>
+          <t>41,92%</t>
         </is>
       </c>
     </row>
@@ -2891,72 +2891,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>86949</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>75848</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>99165</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>61,85%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>53,96%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>70,54%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>117</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>83623</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>73933</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>91904</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>67,6%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>59,77%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>74,3%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>94974</t>
+          <t>79522</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>81535</t>
+          <t>71271</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>106445</t>
+          <t>88205</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>61,26%</t>
+          <t>65,28%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>52,59%</t>
+          <t>58,5%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>68,65%</t>
+          <t>72,41%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>178597</t>
+          <t>166473</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>161907</t>
+          <t>152410</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>193148</t>
+          <t>180256</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>64,07%</t>
+          <t>63,44%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>58,09%</t>
+          <t>58,08%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>69,29%</t>
+          <t>68,7%</t>
         </is>
       </c>
     </row>
@@ -3004,57 +3004,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>140571</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>140571</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>140571</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>174</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>123696</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>123696</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>123696</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>176</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>155044</t>
+          <t>121822</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>155044</t>
+          <t>121822</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>155044</t>
+          <t>121822</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>278740</t>
+          <t>262394</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>278740</t>
+          <t>262394</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>278740</t>
+          <t>262394</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3121,72 +3121,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>80512</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>68894</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>91912</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>51,24%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>43,84%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>58,49%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>81</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>58303</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>48654</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>68192</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>62476</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>52465</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>73917</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
         <is>
           <t>45,31%</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>37,81%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>53,0%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>79228</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>69067</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>89914</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>51,39%</t>
-        </is>
-      </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>44,8%</t>
+          <t>38,05%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>58,33%</t>
+          <t>53,6%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,32 +3196,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>137531</t>
+          <t>142988</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>121661</t>
+          <t>126954</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>152599</t>
+          <t>158941</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>48,63%</t>
+          <t>48,46%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>43,02%</t>
+          <t>43,03%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>53,96%</t>
+          <t>53,87%</t>
         </is>
       </c>
     </row>
@@ -3234,72 +3234,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>76624</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>65224</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>88242</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>48,76%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>41,51%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>56,16%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>103</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>70362</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>60473</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>80011</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>75424</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>63983</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>85435</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
         <is>
           <t>54,69%</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>47,0%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>62,19%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>74931</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>64245</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>85092</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>48,61%</t>
-        </is>
-      </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>41,67%</t>
+          <t>46,4%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>55,2%</t>
+          <t>61,95%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,32 +3309,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>145292</t>
+          <t>152048</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>130224</t>
+          <t>136095</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>161162</t>
+          <t>168082</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>51,37%</t>
+          <t>51,54%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>46,04%</t>
+          <t>46,13%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>56,98%</t>
+          <t>56,97%</t>
         </is>
       </c>
     </row>
@@ -3347,57 +3347,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>157136</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>157136</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>157136</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>184</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>128665</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>128665</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>128665</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>202</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>154159</t>
+          <t>137900</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>154159</t>
+          <t>137900</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>154159</t>
+          <t>137900</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3422,17 +3422,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>282823</t>
+          <t>295036</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>282823</t>
+          <t>295036</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>282823</t>
+          <t>295036</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3464,72 +3464,72 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>332</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>265182</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>241225</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>291196</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>38,61%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>35,12%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>42,4%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>290</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>230130</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>202004</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>287541</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>35,23%</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>30,93%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>44,02%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>332</t>
-        </is>
-      </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>284334</t>
+          <t>211202</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>254866</t>
+          <t>191598</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>315021</t>
+          <t>234513</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>38,18%</t>
+          <t>34,16%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>34,22%</t>
+          <t>30,99%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>42,3%</t>
+          <t>37,93%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,32 +3539,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>514464</t>
+          <t>476384</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>479166</t>
+          <t>444019</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>575961</t>
+          <t>512656</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>36,8%</t>
+          <t>36,5%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>34,28%</t>
+          <t>34,02%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>41,2%</t>
+          <t>39,28%</t>
         </is>
       </c>
     </row>
@@ -3577,72 +3577,72 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>608</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>421642</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>395628</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>445599</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>61,39%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>57,6%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>64,88%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>625</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>423004</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>365593</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>451130</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>64,77%</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>55,98%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>69,07%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>608</t>
-        </is>
-      </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>460399</t>
+          <t>407006</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>429712</t>
+          <t>383695</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>489867</t>
+          <t>426610</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>61,82%</t>
+          <t>65,84%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>57,7%</t>
+          <t>62,07%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>65,78%</t>
+          <t>69,01%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,32 +3652,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>883403</t>
+          <t>828647</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>821906</t>
+          <t>792375</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>918701</t>
+          <t>861012</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>63,2%</t>
+          <t>63,5%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>58,8%</t>
+          <t>60,72%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>65,72%</t>
+          <t>65,98%</t>
         </is>
       </c>
     </row>
@@ -3690,57 +3690,57 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>940</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>915</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>940</t>
-        </is>
-      </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3765,17 +3765,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
